--- a/Softime/TestsCases.xlsx
+++ b/Softime/TestsCases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uli\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35387B68-3A19-4691-B8C2-BC231DF56B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB9835A-D15B-462B-B996-11404626B31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{6D8F5779-0DAF-48EA-A112-025D8B94970F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="263">
   <si>
     <t>Identificador</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>_</t>
   </si>
   <si>
     <t>Modal abierto.</t>
@@ -256,9 +253,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fin de bloque de tareas Release-11</t>
-  </si>
-  <si>
     <t>Verificar alineación de controles</t>
   </si>
   <si>
@@ -320,19 +314,6 @@
   </si>
   <si>
     <t>CP-ENT-002</t>
-  </si>
-  <si>
-    <t>Carga inicial de entidades según usuario</t>
-  </si>
-  <si>
-    <t>Usuario autenticado.</t>
-  </si>
-  <si>
-    <t>1. Abrir listado de entidades.</t>
-  </si>
-  <si>
-    <t>Se muestran únicamente entidades asociadas al usuario.
-No aparecen entidades de otros usuarios.</t>
   </si>
   <si>
     <t>1. Seleccionar un paciente
@@ -562,6 +543,394 @@
     <t>El sistema muestra únicamente las entidades asociadas al paciente seleccionado.
 No se visualizan entidades que pertenezcan a otros pacientes o que no tengan relación con el paciente consultado.
 La cantidad de registros coincide con las relaciones existentes en base de datos.</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>Pantalla principal y modal de Filial-Sector</t>
+  </si>
+  <si>
+    <t>Bloque de tareas 1-5</t>
+  </si>
+  <si>
+    <t>Fin de bloque de tareas 1-5.</t>
+  </si>
+  <si>
+    <t>Bloque de tareas 6-9</t>
+  </si>
+  <si>
+    <t>Fin bloque de tareas 6-9</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Bloque de tareas 10-17</t>
+  </si>
+  <si>
+    <t>Form Modal - Profesional Prescriptor</t>
+  </si>
+  <si>
+    <t>CP-PROF-001</t>
+  </si>
+  <si>
+    <t>CP-PROF-002</t>
+  </si>
+  <si>
+    <t>CP-PROF-003</t>
+  </si>
+  <si>
+    <t>CP-PROF-004</t>
+  </si>
+  <si>
+    <t>CP-PROF-005</t>
+  </si>
+  <si>
+    <t>CP-PROF-006</t>
+  </si>
+  <si>
+    <t>CP-PROF-007</t>
+  </si>
+  <si>
+    <t>Buscar profesional por Tipo de Matrícula y Nro. de Matrícula</t>
+  </si>
+  <si>
+    <t>Existe un profesional registrado con el tipo y número de matrícula ingresados.</t>
+  </si>
+  <si>
+    <t>Tipo de matricula: MN 
+Num matricula: 1234</t>
+  </si>
+  <si>
+    <t>1. Ingresar Tipo de Matrícula.
+2. Ingresar Número de Matrícula.
+3. Ejecutar la búsqueda.</t>
+  </si>
+  <si>
+    <t>Se muestra el profesional correspondiente en la lista de resultados.</t>
+  </si>
+  <si>
+    <t>Búsqueda sin completar ambos filtros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existe al menos un profesional registrado. </t>
+  </si>
+  <si>
+    <t>Tipo de matricula: MN</t>
+  </si>
+  <si>
+    <t>1. Completar solo Tipo de Matrícula.
+2. Ejecutar la búsqueda.</t>
+  </si>
+  <si>
+    <t>Se despliega el buscador extendido de profesionales, con el filtro aplicado a Tipo de matricula, y se visualizarán todos los registros de profesionales con el tipo seleccionado.</t>
+  </si>
+  <si>
+    <t>Búsqueda con datos inexistentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de matricula: MN
+Num matricula: 0000 </t>
+  </si>
+  <si>
+    <t>No existe un profesional registrado con el tipo y número de matrícula ingresados.</t>
+  </si>
+  <si>
+    <t>1. Ingresar un Tipo y Número de Matrícula inexistentes.
+2. Ejecutar la búsqueda.</t>
+  </si>
+  <si>
+    <t>Se muestra mensaje "Sin resultados".</t>
+  </si>
+  <si>
+    <t>Seleccionar un profesional desde la búsqueda</t>
+  </si>
+  <si>
+    <t>1. Buscar un profesional.
+2. Seleccionarlo.</t>
+  </si>
+  <si>
+    <t>Realizar una búsqueda con datos válidos y registrados</t>
+  </si>
+  <si>
+    <t>El modal se cierra.
+Se carga el profesional seleccionado en el formulario principal.
+Queda almacenado el ID del profesional.</t>
+  </si>
+  <si>
+    <t>Eliminar profesional seleccionado</t>
+  </si>
+  <si>
+    <t>Seleccionar un profesional.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar un profesional.
+2. Presionar ícono de borrar.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Se elimina la selección.
+El formulario vuelve al estado inicial.</t>
+  </si>
+  <si>
+    <t>Carga de profesional al editar un registro</t>
+  </si>
+  <si>
+    <t>Existe un registro con profesional asociado.</t>
+  </si>
+  <si>
+    <t>El formulario muestra el profesional previamente guardado.</t>
+  </si>
+  <si>
+    <t>1. Abrir modal de ingreso ya registrado.
+2. Identificar el campo de profesional asociado.</t>
+  </si>
+  <si>
+    <t>Alta de profesional</t>
+  </si>
+  <si>
+    <t>1. Completar todos los datos requeridos.
+2. Guardar.</t>
+  </si>
+  <si>
+    <t>El profesional se crea correctamente.
+El modal se cierra.
+El profesional queda seleccionado en el formulario principal.</t>
+  </si>
+  <si>
+    <t>No existe registro previo con los datos a utilizar.</t>
+  </si>
+  <si>
+    <t>Tipo de matricula: MN
+Num matricula: 2233 
+DNI: 11223344</t>
+  </si>
+  <si>
+    <t>CP-PROF-008</t>
+  </si>
+  <si>
+    <t>CP-PROF-009</t>
+  </si>
+  <si>
+    <t>CP-PROF-010</t>
+  </si>
+  <si>
+    <t>Alta con campos obligatorios incompletos</t>
+  </si>
+  <si>
+    <t>El sistema informa los campos faltantes.
+No se crea el profesional.</t>
+  </si>
+  <si>
+    <t>1. Procurar dejar campos requeridos sin completar.</t>
+  </si>
+  <si>
+    <t>Se validó la obligatoriedad de los campos marcados como requeridos.</t>
+  </si>
+  <si>
+    <t>Filtrado parcial en buscadores</t>
+  </si>
+  <si>
+    <t>Num matricula: 12</t>
+  </si>
+  <si>
+    <t>1. Ingresar parte del numero de matricula.</t>
+  </si>
+  <si>
+    <t>La lista se filtra correctamente.</t>
+  </si>
+  <si>
+    <t>Persistencia del ProfesionalID</t>
+  </si>
+  <si>
+    <t>El POST envía el ID del profesional seleccionado.</t>
+  </si>
+  <si>
+    <t>1. Abrir Devtools -&gt; Headers.
+2. Verificar que la URL envie el ProfesionalID correspondiente.</t>
+  </si>
+  <si>
+    <t>Diagnósticos</t>
+  </si>
+  <si>
+    <t>CP-DIAG-001</t>
+  </si>
+  <si>
+    <t>CP-DIAG-002</t>
+  </si>
+  <si>
+    <t>CP-DIAG-003</t>
+  </si>
+  <si>
+    <t>Filtrado parcial de diagnósticos</t>
+  </si>
+  <si>
+    <t>Modal de Ingreso abierto.</t>
+  </si>
+  <si>
+    <t>Se muestran únicamente los diagnósticos coincidentes.</t>
+  </si>
+  <si>
+    <t>1. Escribir parcialmente palabras, letras o codigos identificadores de diagnostico.</t>
+  </si>
+  <si>
+    <t>Apertura de registro existente con diagnóstico</t>
+  </si>
+  <si>
+    <t>Existe un registro guardado con diagnóstico y subdiagnóstico.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar un ingreso.
+2. Desplegar el diagnóstico y subdiagnóstico.</t>
+  </si>
+  <si>
+    <t>Se mapean correctamente los datos asociados al paciente.</t>
+  </si>
+  <si>
+    <t>Guardado y recuperación de diagnóstico/subdiagnóstico</t>
+  </si>
+  <si>
+    <t>1. Crear un nuevo ingreso.
+2. Asociar un diagnóstico y subdiagnóstico.
+3. Guardar.
+4. Abrir el ingreso creado.</t>
+  </si>
+  <si>
+    <t>Los datos asociados muestran persistencia.</t>
+  </si>
+  <si>
+    <t>Prestaciones</t>
+  </si>
+  <si>
+    <t>CP-PRES-001</t>
+  </si>
+  <si>
+    <t>Carga del combo de prestaciones</t>
+  </si>
+  <si>
+    <t>Devtools abierto</t>
+  </si>
+  <si>
+    <t>1. Verificar el servicio GET.</t>
+  </si>
+  <si>
+    <t>El combo carga las prestaciones disponibles.</t>
+  </si>
+  <si>
+    <t>CP-PRES-002</t>
+  </si>
+  <si>
+    <t>CP-PRES-003</t>
+  </si>
+  <si>
+    <t>Autofiltrado del combo de prestaciones</t>
+  </si>
+  <si>
+    <t>1. Escribir parte del nombre de una prestación.</t>
+  </si>
+  <si>
+    <t>Se filtran las opciones coincidentes.</t>
+  </si>
+  <si>
+    <t>Selección de prestación</t>
+  </si>
+  <si>
+    <t>La prestación seleccionada se guarda correctamente.</t>
+  </si>
+  <si>
+    <t>1. Verificar que la prestación quede asociada al registro.</t>
+  </si>
+  <si>
+    <t>CP-PRES-004</t>
+  </si>
+  <si>
+    <t>Manejo de error del servicio de prestaciones</t>
+  </si>
+  <si>
+    <t>Se informa el error al usuario.
+El formulario continúa siendo utilizable.</t>
+  </si>
+  <si>
+    <t>Selector de prestaciones desplegado.</t>
+  </si>
+  <si>
+    <t>Input: Prestacion de prueba</t>
+  </si>
+  <si>
+    <t>1. Realizar el input.
+2. Confirmar el input como prestacion seleccionada</t>
+  </si>
+  <si>
+    <t>Apertura del modal de instituciones médicas</t>
+  </si>
+  <si>
+    <t>El paciente existe.</t>
+  </si>
+  <si>
+    <t>Verificar datos de la grilla</t>
+  </si>
+  <si>
+    <t>Devtools abierto.</t>
+  </si>
+  <si>
+    <t>1. Abrir el modal.
+2. Comparar los datos mostrados con la información del endpoint.</t>
+  </si>
+  <si>
+    <t>La lista coincide con las relaciones existentes del paciente.</t>
+  </si>
+  <si>
+    <t>1. Abrir el modal de agregar.</t>
+  </si>
+  <si>
+    <t>CP-ENT-004</t>
+  </si>
+  <si>
+    <t>CP-ENT-005</t>
+  </si>
+  <si>
+    <t>1. Abrir la pantalla del paciente.
+2. Presionar el botón para administrar entidades médicas.</t>
+  </si>
+  <si>
+    <t>Se abre el modal.
+Se muestra la lista de entidades médicas relacionadas con el paciente.</t>
+  </si>
+  <si>
+    <t>Verificar datos enviados en el POST</t>
+  </si>
+  <si>
+    <t>1. Abrir Devtools.
+2. Agregar una institución.
+3. Inspeccionar el request.</t>
+  </si>
+  <si>
+    <t>Se envían únicamente los datos mínimos requeridos para crear la relación.</t>
+  </si>
+  <si>
+    <t>CP-ENT-006</t>
+  </si>
+  <si>
+    <t>El paciente puede tener o no entidades asociadas.</t>
+  </si>
+  <si>
+    <t>El paciente tiene entidades asociadas.</t>
+  </si>
+  <si>
+    <t>Verificar filtrado de entidades ya vinculadas</t>
+  </si>
+  <si>
+    <t>No se muestran las instituciones ya relacionadas con el paciente.
+Solo aparecen las entidades disponibles para agregar.</t>
+  </si>
+  <si>
+    <t>Fin bloque de tareas 10-17</t>
+  </si>
+  <si>
+    <t>Bloque de tareas 18-31</t>
   </si>
 </sst>
 </file>
@@ -637,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -648,6 +1017,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,10 +1036,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -986,735 +1355,1465 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D8BD5B-5AC0-464D-A735-C3D164C9EF96}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="48.28515625" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" customWidth="1"/>
+    <col min="8" max="8" width="48.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3"/>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>182</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>41</v>
+        <v>182</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>44</v>
+        <v>182</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
       </c>
       <c r="E8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I10" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="E11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F19" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="G19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>182</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>182</v>
+      </c>
+      <c r="F21" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="G22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>182</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E25" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="E27" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E28" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" t="s">
+        <v>258</v>
+      </c>
+      <c r="E29" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E30" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31"/>
+      <c r="D31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="3"/>
+      <c r="I38" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" t="s">
+        <v>182</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>182</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" t="s">
+        <v>126</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" t="s">
+        <v>182</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25"/>
-      <c r="C25" s="3"/>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" t="s">
-        <v>131</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G34" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>125</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>144</v>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" t="s">
+        <v>166</v>
+      </c>
+      <c r="E48" t="s">
+        <v>167</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" t="s">
+        <v>174</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>157</v>
+      </c>
+      <c r="C51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>207</v>
+      </c>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>210</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>222</v>
+      </c>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>228</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>229</v>
+      </c>
+      <c r="C67" t="s">
+        <v>233</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H67" t="s">
+        <v>234</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>236</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
